--- a/Team-Data/2012-13/2-23-2012-13.xlsx
+++ b/Team-Data/2012-13/2-23-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
         <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>0.574</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
@@ -679,46 +746,46 @@
         <v>37.4</v>
       </c>
       <c r="J2" t="n">
-        <v>81</v>
+        <v>80.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L2" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>23.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.383</v>
+        <v>0.38</v>
       </c>
       <c r="O2" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="P2" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.701</v>
+        <v>0.7</v>
       </c>
       <c r="R2" t="n">
         <v>9.5</v>
       </c>
       <c r="S2" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T2" t="n">
         <v>40.9</v>
       </c>
       <c r="U2" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="V2" t="n">
         <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X2" t="n">
         <v>4.9</v>
@@ -730,19 +797,19 @@
         <v>18.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.40000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="AC2" t="n">
         <v>0.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
@@ -757,7 +824,7 @@
         <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK2" t="n">
         <v>7</v>
@@ -769,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
         <v>28</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AW2" t="n">
         <v>15</v>
@@ -802,7 +869,7 @@
         <v>19</v>
       </c>
       <c r="AY2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
@@ -811,7 +878,7 @@
         <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
@@ -936,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ3" t="n">
         <v>26</v>
@@ -945,7 +1012,7 @@
         <v>8</v>
       </c>
       <c r="AL3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM3" t="n">
         <v>26</v>
@@ -963,7 +1030,7 @@
         <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
@@ -978,10 +1045,10 @@
         <v>9</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>0.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
         <v>8</v>
@@ -1157,7 +1224,7 @@
         <v>27</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
         <v>23</v>
@@ -1166,7 +1233,7 @@
         <v>20</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ4" t="n">
         <v>3</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -1207,19 +1274,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" t="n">
         <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.232</v>
+        <v>0.236</v>
       </c>
       <c r="H5" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I5" t="n">
         <v>34.3</v>
@@ -1234,25 +1301,25 @@
         <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O5" t="n">
         <v>19.4</v>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Q5" t="n">
         <v>0.748</v>
       </c>
       <c r="R5" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S5" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T5" t="n">
         <v>41.2</v>
@@ -1261,31 +1328,31 @@
         <v>18.9</v>
       </c>
       <c r="V5" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W5" t="n">
         <v>7.1</v>
       </c>
       <c r="X5" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="Z5" t="n">
         <v>19.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.8</v>
+        <v>93.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-8.9</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1297,7 +1364,7 @@
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
@@ -1309,13 +1376,13 @@
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM5" t="n">
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1357,7 +1424,7 @@
         <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>1.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
@@ -1515,13 +1582,13 @@
         <v>13</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU6" t="n">
         <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
@@ -1533,7 +1600,7 @@
         <v>22</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
         <v>14</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -1571,61 +1638,61 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" t="n">
         <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>0.327</v>
+        <v>0.315</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J7" t="n">
         <v>84.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.432</v>
+        <v>0.43</v>
       </c>
       <c r="L7" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M7" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O7" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P7" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.761</v>
+        <v>0.759</v>
       </c>
       <c r="R7" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S7" t="n">
         <v>28.4</v>
       </c>
       <c r="T7" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U7" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V7" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W7" t="n">
         <v>8.199999999999999</v>
@@ -1643,28 +1710,28 @@
         <v>20.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>97.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.6</v>
+        <v>-4.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
         <v>24</v>
       </c>
       <c r="AG7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH7" t="n">
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ7" t="n">
         <v>3</v>
@@ -1688,19 +1755,19 @@
         <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV7" t="n">
         <v>7</v>
@@ -1721,10 +1788,10 @@
         <v>11</v>
       </c>
       <c r="BB7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BC7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-1</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
@@ -1891,7 +1958,7 @@
         <v>16</v>
       </c>
       <c r="AX8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
         <v>6</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>0.614</v>
+        <v>0.607</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
@@ -1956,7 +2023,7 @@
         <v>85.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.472</v>
+        <v>0.471</v>
       </c>
       <c r="L9" t="n">
         <v>6.5</v>
@@ -1965,28 +2032,28 @@
         <v>19.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O9" t="n">
         <v>18.2</v>
       </c>
       <c r="P9" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="R9" t="n">
         <v>13.5</v>
       </c>
       <c r="S9" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T9" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="V9" t="n">
         <v>15.3</v>
@@ -1995,25 +2062,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="X9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y9" t="n">
         <v>6.6</v>
       </c>
-      <c r="Y9" t="n">
-        <v>6.7</v>
-      </c>
       <c r="Z9" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA9" t="n">
         <v>22.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>105.2</v>
+        <v>105.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>6</v>
@@ -2025,7 +2092,7 @@
         <v>8</v>
       </c>
       <c r="AH9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2040,7 +2107,7 @@
         <v>18</v>
       </c>
       <c r="AM9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN9" t="n">
         <v>26</v>
@@ -2055,7 +2122,7 @@
         <v>30</v>
       </c>
       <c r="AR9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS9" t="n">
         <v>10</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW9" t="n">
         <v>3</v>
@@ -2079,7 +2146,7 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -2117,37 +2184,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" t="n">
         <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>0.379</v>
+        <v>0.386</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J10" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.443</v>
+        <v>0.445</v>
       </c>
       <c r="L10" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M10" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N10" t="n">
-        <v>0.362</v>
+        <v>0.365</v>
       </c>
       <c r="O10" t="n">
         <v>16.3</v>
@@ -2156,7 +2223,7 @@
         <v>23.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.694</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R10" t="n">
         <v>12.6</v>
@@ -2165,16 +2232,16 @@
         <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U10" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X10" t="n">
         <v>5.6</v>
@@ -2186,13 +2253,13 @@
         <v>19.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.6</v>
+        <v>-2.3</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -2204,31 +2271,31 @@
         <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH10" t="n">
         <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="n">
         <v>18</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM10" t="n">
         <v>25</v>
       </c>
       <c r="AN10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2237,7 +2304,7 @@
         <v>29</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
         <v>14</v>
@@ -2255,19 +2322,19 @@
         <v>27</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>10</v>
       </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2392,7 +2459,7 @@
         <v>12</v>
       </c>
       <c r="AI11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
         <v>7</v>
@@ -2443,7 +2510,7 @@
         <v>18</v>
       </c>
       <c r="AZ11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA11" t="n">
         <v>22</v>
@@ -2452,7 +2519,7 @@
         <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" t="n">
         <v>31</v>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>0.534</v>
+        <v>0.544</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2499,43 +2566,43 @@
         <v>38.5</v>
       </c>
       <c r="J12" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.463</v>
       </c>
       <c r="L12" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="M12" t="n">
-        <v>28.7</v>
+        <v>28.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O12" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="R12" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S12" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U12" t="n">
         <v>23.3</v>
       </c>
       <c r="V12" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W12" t="n">
         <v>8.4</v>
@@ -2550,13 +2617,13 @@
         <v>20.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.3</v>
+        <v>106.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -2565,7 +2632,7 @@
         <v>12</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
         <v>14</v>
@@ -2592,7 +2659,7 @@
         <v>9</v>
       </c>
       <c r="AO12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP12" t="n">
         <v>6</v>
@@ -2601,13 +2668,13 @@
         <v>16</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU12" t="n">
         <v>4</v>
@@ -2616,7 +2683,7 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX12" t="n">
         <v>27</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -2663,25 +2730,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F13" t="n">
         <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>0.625</v>
+        <v>0.618</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J13" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K13" t="n">
         <v>0.433</v>
@@ -2690,7 +2757,7 @@
         <v>6.9</v>
       </c>
       <c r="M13" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N13" t="n">
         <v>0.355</v>
@@ -2699,16 +2766,16 @@
         <v>16.8</v>
       </c>
       <c r="P13" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q13" t="n">
         <v>0.741</v>
       </c>
       <c r="R13" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S13" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T13" t="n">
         <v>46</v>
@@ -2717,7 +2784,7 @@
         <v>20.5</v>
       </c>
       <c r="V13" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
         <v>6.9</v>
@@ -2726,22 +2793,22 @@
         <v>6.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA13" t="n">
         <v>21.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.7</v>
+        <v>93.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
         <v>6</v>
@@ -2759,7 +2826,7 @@
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
@@ -2774,7 +2841,7 @@
         <v>13</v>
       </c>
       <c r="AO13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP13" t="n">
         <v>13</v>
@@ -2792,10 +2859,10 @@
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>26</v>
@@ -2804,7 +2871,7 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
@@ -2813,7 +2880,7 @@
         <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -2845,22 +2912,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" t="n">
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J14" t="n">
         <v>80.59999999999999</v>
@@ -2869,7 +2936,7 @@
         <v>0.473</v>
       </c>
       <c r="L14" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M14" t="n">
         <v>20.3</v>
@@ -2884,13 +2951,13 @@
         <v>23.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.708</v>
+        <v>0.706</v>
       </c>
       <c r="R14" t="n">
         <v>11.6</v>
       </c>
       <c r="S14" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T14" t="n">
         <v>41.8</v>
@@ -2899,34 +2966,34 @@
         <v>23.3</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W14" t="n">
         <v>9.9</v>
       </c>
       <c r="X14" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y14" t="n">
         <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA14" t="n">
         <v>21.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>100.4</v>
+        <v>100.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>4</v>
@@ -2938,7 +3005,7 @@
         <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ14" t="n">
         <v>25</v>
@@ -2956,7 +3023,7 @@
         <v>12</v>
       </c>
       <c r="AO14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP14" t="n">
         <v>9</v>
@@ -2974,10 +3041,10 @@
         <v>17</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>16</v>
@@ -3114,7 +3181,7 @@
         <v>17</v>
       </c>
       <c r="AG15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH15" t="n">
         <v>29</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
         <v>3</v>
@@ -3156,13 +3223,13 @@
         <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV15" t="n">
         <v>26</v>
       </c>
       <c r="AW15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX15" t="n">
         <v>13</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
@@ -3320,7 +3387,7 @@
         <v>24</v>
       </c>
       <c r="AO16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP16" t="n">
         <v>24</v>
@@ -3329,13 +3396,13 @@
         <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS16" t="n">
         <v>27</v>
       </c>
       <c r="AT16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU16" t="n">
         <v>23</v>
@@ -3353,7 +3420,7 @@
         <v>21</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -3391,82 +3458,82 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.736</v>
+        <v>0.731</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
       </c>
       <c r="I17" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="J17" t="n">
         <v>78.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.495</v>
+        <v>0.493</v>
       </c>
       <c r="L17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M17" t="n">
         <v>21.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.386</v>
+        <v>0.385</v>
       </c>
       <c r="O17" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P17" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R17" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="S17" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T17" t="n">
         <v>38.7</v>
       </c>
       <c r="U17" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V17" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="W17" t="n">
         <v>8.6</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.1</v>
+        <v>102.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="AD17" t="n">
         <v>27</v>
@@ -3511,7 +3578,7 @@
         <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS17" t="n">
         <v>20</v>
@@ -3526,19 +3593,19 @@
         <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA17" t="n">
         <v>12</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>13</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" t="n">
         <v>26</v>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" t="n">
-        <v>0.481</v>
+        <v>0.491</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
@@ -3597,10 +3664,10 @@
         <v>0.434</v>
       </c>
       <c r="L18" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M18" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="N18" t="n">
         <v>0.348</v>
@@ -3612,46 +3679,46 @@
         <v>21.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.732</v>
+        <v>0.731</v>
       </c>
       <c r="R18" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S18" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="T18" t="n">
-        <v>43.8</v>
+        <v>43.5</v>
       </c>
       <c r="U18" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V18" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W18" t="n">
         <v>8.4</v>
       </c>
       <c r="X18" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="Y18" t="n">
         <v>4.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA18" t="n">
         <v>19.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC18" t="n">
         <v>-1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
@@ -3660,7 +3727,7 @@
         <v>16</v>
       </c>
       <c r="AG18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH18" t="n">
         <v>22</v>
@@ -3681,7 +3748,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
         <v>24</v>
@@ -3696,28 +3763,28 @@
         <v>3</v>
       </c>
       <c r="AS18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV18" t="n">
         <v>8</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>9</v>
       </c>
       <c r="BA18" t="n">
         <v>19</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
         <v>23</v>
@@ -3842,7 +3909,7 @@
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH19" t="n">
         <v>27</v>
@@ -3866,7 +3933,7 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP19" t="n">
         <v>5</v>
@@ -3881,10 +3948,10 @@
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV19" t="n">
         <v>25</v>
@@ -3893,7 +3960,7 @@
         <v>14</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY19" t="n">
         <v>24</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>24</v>
@@ -4030,13 +4097,13 @@
         <v>19</v>
       </c>
       <c r="AI20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>16</v>
@@ -4054,7 +4121,7 @@
         <v>27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>16</v>
@@ -4063,13 +4130,13 @@
         <v>21</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU20" t="n">
         <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
         <v>29</v>
@@ -4081,7 +4148,7 @@
         <v>25</v>
       </c>
       <c r="AZ20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>3.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE21" t="n">
         <v>9</v>
@@ -4212,13 +4279,13 @@
         <v>27</v>
       </c>
       <c r="AI21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ21" t="n">
         <v>12</v>
       </c>
       <c r="AK21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4245,7 +4312,7 @@
         <v>22</v>
       </c>
       <c r="AT21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU21" t="n">
         <v>29</v>
@@ -4263,7 +4330,7 @@
         <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA21" t="n">
         <v>20</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4427,7 +4494,7 @@
         <v>6</v>
       </c>
       <c r="AT22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU22" t="n">
         <v>17</v>
@@ -4436,10 +4503,10 @@
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY22" t="n">
         <v>4</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E23" t="n">
         <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G23" t="n">
-        <v>0.268</v>
+        <v>0.273</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
@@ -4501,43 +4568,43 @@
         <v>37.6</v>
       </c>
       <c r="J23" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L23" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M23" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="O23" t="n">
         <v>12.1</v>
       </c>
       <c r="P23" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.766</v>
+        <v>0.769</v>
       </c>
       <c r="R23" t="n">
         <v>10.7</v>
       </c>
       <c r="S23" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T23" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U23" t="n">
         <v>23.2</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W23" t="n">
         <v>6</v>
@@ -4549,7 +4616,7 @@
         <v>5</v>
       </c>
       <c r="Z23" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA23" t="n">
         <v>16.3</v>
@@ -4558,10 +4625,10 @@
         <v>93.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6</v>
+        <v>-5.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4588,7 +4655,7 @@
         <v>20</v>
       </c>
       <c r="AM23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN23" t="n">
         <v>28</v>
@@ -4600,16 +4667,16 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU23" t="n">
         <v>7</v>
@@ -4621,19 +4688,19 @@
         <v>30</v>
       </c>
       <c r="AX23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY23" t="n">
         <v>15</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>28</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E24" t="n">
         <v>22</v>
       </c>
       <c r="F24" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G24" t="n">
-        <v>0.415</v>
+        <v>0.423</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4683,64 +4750,64 @@
         <v>37</v>
       </c>
       <c r="J24" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0.442</v>
       </c>
       <c r="L24" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M24" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="P24" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.72</v>
+        <v>0.718</v>
       </c>
       <c r="R24" t="n">
         <v>10.8</v>
       </c>
       <c r="S24" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.5</v>
       </c>
       <c r="U24" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V24" t="n">
         <v>12.9</v>
       </c>
       <c r="W24" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="AB24" t="n">
         <v>92.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.5</v>
+        <v>-3.2</v>
       </c>
       <c r="AD24" t="n">
         <v>27</v>
@@ -4749,7 +4816,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG24" t="n">
         <v>20</v>
@@ -4767,13 +4834,13 @@
         <v>20</v>
       </c>
       <c r="AL24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AM24" t="n">
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4785,13 +4852,13 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AU24" t="n">
         <v>13</v>
@@ -4800,7 +4867,7 @@
         <v>2</v>
       </c>
       <c r="AW24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX24" t="n">
         <v>16</v>
@@ -4809,7 +4876,7 @@
         <v>11</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>26</v>
@@ -4934,10 +5001,10 @@
         <v>28</v>
       </c>
       <c r="AG25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
         <v>13</v>
@@ -4946,7 +5013,7 @@
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL25" t="n">
         <v>27</v>
@@ -4976,7 +5043,7 @@
         <v>22</v>
       </c>
       <c r="AU25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV25" t="n">
         <v>14</v>
@@ -4991,13 +5058,13 @@
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA25" t="n">
         <v>28</v>
       </c>
       <c r="BB25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-3</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5122,7 +5189,7 @@
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ26" t="n">
         <v>14</v>
@@ -5140,7 +5207,7 @@
         <v>27</v>
       </c>
       <c r="AO26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="n">
         <v>23</v>
@@ -5155,7 +5222,7 @@
         <v>18</v>
       </c>
       <c r="AT26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU26" t="n">
         <v>22</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-7.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5328,7 +5395,7 @@
         <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR27" t="n">
         <v>11</v>
@@ -5343,13 +5410,13 @@
         <v>28</v>
       </c>
       <c r="AV27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW27" t="n">
         <v>11</v>
       </c>
       <c r="AX27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
@@ -5358,10 +5425,10 @@
         <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5501,7 +5568,7 @@
         <v>6</v>
       </c>
       <c r="AN28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO28" t="n">
         <v>16</v>
@@ -5519,7 +5586,7 @@
         <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5668,7 +5735,7 @@
         <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ29" t="n">
         <v>15</v>
@@ -5725,7 +5792,7 @@
         <v>18</v>
       </c>
       <c r="BB29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -5757,22 +5824,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E30" t="n">
         <v>31</v>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>0.554</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J30" t="n">
         <v>81.7</v>
@@ -5781,22 +5848,22 @@
         <v>0.452</v>
       </c>
       <c r="L30" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M30" t="n">
         <v>16.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="O30" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P30" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R30" t="n">
         <v>12.2</v>
@@ -5808,7 +5875,7 @@
         <v>41.9</v>
       </c>
       <c r="U30" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V30" t="n">
         <v>14.8</v>
@@ -5820,22 +5887,22 @@
         <v>6.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
         <v>21.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE30" t="n">
         <v>12</v>
@@ -5847,25 +5914,25 @@
         <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ30" t="n">
         <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM30" t="n">
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5874,7 +5941,7 @@
         <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR30" t="n">
         <v>10</v>
@@ -5889,7 +5956,7 @@
         <v>11</v>
       </c>
       <c r="AV30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW30" t="n">
         <v>10</v>
@@ -5910,7 +5977,7 @@
         <v>11</v>
       </c>
       <c r="BC30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F31" t="n">
         <v>37</v>
       </c>
       <c r="G31" t="n">
-        <v>0.315</v>
+        <v>0.302</v>
       </c>
       <c r="H31" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I31" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J31" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.43</v>
+        <v>0.428</v>
       </c>
       <c r="L31" t="n">
         <v>6.5</v>
@@ -5969,7 +6036,7 @@
         <v>18.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="O31" t="n">
         <v>14.7</v>
@@ -5978,19 +6045,19 @@
         <v>20</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.736</v>
+        <v>0.734</v>
       </c>
       <c r="R31" t="n">
         <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T31" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U31" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V31" t="n">
         <v>15.5</v>
@@ -6005,19 +6072,19 @@
         <v>4.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
         <v>18.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>92</v>
+        <v>91.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.7</v>
+        <v>-3.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6047,7 +6114,7 @@
         <v>18</v>
       </c>
       <c r="AN31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="n">
         <v>26</v>
@@ -6059,16 +6126,16 @@
         <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV31" t="n">
         <v>28</v>
@@ -6092,7 +6159,7 @@
         <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-23-2012-13</t>
+          <t>2013-02-23</t>
         </is>
       </c>
     </row>
